--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_hp_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_hp_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -812,7 +812,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>30-01-2021 08:30</t>
+          <t>2021-01-30 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T38" t="inlineStr"/>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
@@ -4160,7 +4160,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>30-01-2021 08:30</t>
+          <t>2021-01-30 08:30:00</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
@@ -4439,7 +4439,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>03-01-2021 08:30</t>
+          <t>2021-03-01 08:30:00</t>
         </is>
       </c>
       <c r="T43" t="inlineStr"/>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T44" t="inlineStr"/>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>30-01-2021 08:30</t>
+          <t>2021-01-30 08:30:00</t>
         </is>
       </c>
       <c r="T46" t="inlineStr"/>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>13-02-2021 08:30</t>
+          <t>2021-02-13 08:30:00</t>
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T48" t="inlineStr"/>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T54" t="inlineStr"/>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T55" t="inlineStr"/>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T56" t="inlineStr"/>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T57" t="inlineStr"/>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>30-01-2021 08:30</t>
+          <t>2021-01-30 08:30:00</t>
         </is>
       </c>
       <c r="T58" t="inlineStr"/>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T59" t="inlineStr"/>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T60" t="inlineStr"/>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T61" t="inlineStr"/>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T62" t="inlineStr"/>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T63" t="inlineStr"/>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T64" t="inlineStr"/>
@@ -6485,7 +6485,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T65" t="inlineStr"/>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T66" t="inlineStr"/>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>30-01-2021 08:30</t>
+          <t>2021-01-30 08:30:00</t>
         </is>
       </c>
       <c r="T67" t="inlineStr"/>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T68" t="inlineStr"/>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T69" t="inlineStr"/>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T70" t="inlineStr"/>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T71" t="inlineStr"/>
@@ -7136,7 +7136,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T72" t="inlineStr"/>
@@ -7229,7 +7229,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T73" t="inlineStr"/>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T74" t="inlineStr"/>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T75" t="inlineStr"/>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T76" t="inlineStr"/>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T77" t="inlineStr"/>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T78" t="inlineStr"/>
@@ -7787,7 +7787,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T79" t="n">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>20-10-2021 08:30</t>
+          <t>2021-10-20 08:30:00</t>
         </is>
       </c>
       <c r="T80" t="n">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T81" t="inlineStr"/>
@@ -8078,7 +8078,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T82" t="inlineStr"/>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T83" t="inlineStr"/>
@@ -8264,7 +8264,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>09-01-2021 08:30</t>
+          <t>2021-09-01 08:30:00</t>
         </is>
       </c>
       <c r="T84" t="inlineStr"/>
@@ -8357,7 +8357,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>14-02-2021 08:30</t>
+          <t>2021-02-14 08:30:00</t>
         </is>
       </c>
       <c r="T85" t="inlineStr"/>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T86" t="inlineStr"/>
@@ -8543,7 +8543,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>03-01-2021 08:30</t>
+          <t>2021-03-01 08:30:00</t>
         </is>
       </c>
       <c r="T87" t="inlineStr"/>
@@ -8636,7 +8636,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>07-02-2021 08:30</t>
+          <t>2021-07-02 08:30:00</t>
         </is>
       </c>
       <c r="T88" t="inlineStr"/>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T89" t="inlineStr"/>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>10-01-2021 08:30</t>
+          <t>2021-10-01 08:30:00</t>
         </is>
       </c>
       <c r="T90" t="inlineStr"/>
@@ -8915,7 +8915,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T91" t="inlineStr"/>
@@ -9008,7 +9008,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T92" t="inlineStr"/>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T93" t="inlineStr"/>
@@ -9194,7 +9194,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T94" t="inlineStr"/>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T95" t="inlineStr"/>
@@ -9380,7 +9380,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T96" t="inlineStr"/>
@@ -9473,7 +9473,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T97" t="inlineStr"/>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T98" t="inlineStr"/>
@@ -9659,7 +9659,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T99" t="inlineStr"/>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T100" t="inlineStr"/>
@@ -9845,7 +9845,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T101" t="inlineStr"/>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T102" t="inlineStr"/>
@@ -10031,7 +10031,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T103" t="inlineStr"/>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T104" t="inlineStr"/>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T105" t="inlineStr"/>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T106" t="inlineStr"/>
@@ -10403,7 +10403,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T107" t="inlineStr"/>
@@ -10496,7 +10496,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T108" t="inlineStr"/>
@@ -10589,7 +10589,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T109" t="inlineStr"/>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T110" t="inlineStr"/>
@@ -10775,7 +10775,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T111" t="inlineStr"/>
@@ -10868,7 +10868,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T112" t="inlineStr"/>
@@ -10961,7 +10961,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T113" t="inlineStr"/>
@@ -11054,7 +11054,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T114" t="n">
@@ -11153,7 +11153,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T115" t="n">
@@ -11252,7 +11252,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T116" t="n">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T117" t="n">
@@ -11450,7 +11450,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T118" t="n">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>03-01-2021 08:30</t>
+          <t>2021-03-01 08:30:00</t>
         </is>
       </c>
       <c r="T119" t="n">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T120" t="n">
@@ -11747,7 +11747,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T121" t="n">
@@ -11846,7 +11846,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T122" t="n">
@@ -11947,7 +11947,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T123" t="n">
@@ -12046,7 +12046,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T124" t="n">
@@ -12145,7 +12145,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T125" t="n">
@@ -12244,7 +12244,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T126" t="n">
@@ -12343,7 +12343,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T127" t="n">
@@ -12442,7 +12442,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T128" t="n">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T129" t="n">
@@ -12640,7 +12640,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>13-10-2021 08:30</t>
+          <t>2021-10-13 08:30:00</t>
         </is>
       </c>
       <c r="T130" t="n">
@@ -12739,7 +12739,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T131" t="n">
@@ -12838,7 +12838,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T132" t="n">
@@ -12937,7 +12937,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T133" t="n">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T134" t="n">
@@ -13135,7 +13135,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T135" t="n">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T136" t="n">
@@ -13335,7 +13335,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T137" t="n">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>25-05-2021 08:30</t>
+          <t>2021-05-25 08:30:00</t>
         </is>
       </c>
       <c r="T138" t="n">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T139" t="n">
@@ -13638,7 +13638,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T140" t="n">
@@ -13739,7 +13739,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T141" t="n">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T142" t="n">
@@ -13937,7 +13937,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>13-10-2021 08:30</t>
+          <t>2021-10-13 08:30:00</t>
         </is>
       </c>
       <c r="T143" t="n">
@@ -14036,7 +14036,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T144" t="n">
@@ -14135,7 +14135,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>13-10-2021 08:30</t>
+          <t>2021-10-13 08:30:00</t>
         </is>
       </c>
       <c r="T145" t="n">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T146" t="n">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T147" t="n">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T148" t="n">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T149" t="n">
@@ -14636,7 +14636,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T150" t="n">
@@ -14735,7 +14735,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>20-10-2021 08:30</t>
+          <t>2021-10-20 08:30:00</t>
         </is>
       </c>
       <c r="T151" t="n">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T152" t="n">
@@ -14933,7 +14933,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T153" t="n">
@@ -15032,7 +15032,7 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T154" t="n">
@@ -15131,7 +15131,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T155" t="n">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>30-01-2021 08:30</t>
+          <t>2021-01-30 08:30:00</t>
         </is>
       </c>
       <c r="T156" t="n">
@@ -15333,7 +15333,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T157" t="n">
@@ -15434,7 +15434,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T158" t="n">
@@ -15535,7 +15535,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>13-10-2021 08:30</t>
+          <t>2021-10-13 08:30:00</t>
         </is>
       </c>
       <c r="T159" t="n">
@@ -15636,7 +15636,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T160" t="n">
@@ -15735,7 +15735,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T161" t="n">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>10-04-2021 08:30</t>
+          <t>2021-10-04 08:30:00</t>
         </is>
       </c>
       <c r="T162" t="n">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>19-10-2021 08:30</t>
+          <t>2021-10-19 08:30:00</t>
         </is>
       </c>
       <c r="T163" t="n">
@@ -16036,7 +16036,7 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T164" t="n">
@@ -16135,7 +16135,7 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T165" t="n">
@@ -16234,7 +16234,7 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>13-10-2021 08:30</t>
+          <t>2021-10-13 08:30:00</t>
         </is>
       </c>
       <c r="T166" t="n">
@@ -16333,7 +16333,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>16-12-2021 08:30</t>
+          <t>2021-12-16 08:30:00</t>
         </is>
       </c>
       <c r="T167" t="n">
@@ -16434,7 +16434,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T168" t="n">
@@ -16533,7 +16533,7 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>13-10-2021 08:30</t>
+          <t>2021-10-13 08:30:00</t>
         </is>
       </c>
       <c r="T169" t="n">
@@ -16634,7 +16634,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T170" t="n">
@@ -16735,7 +16735,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T171" t="n">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T172" t="n">
@@ -16935,7 +16935,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>16-10-2021 08:30</t>
+          <t>2021-10-16 08:30:00</t>
         </is>
       </c>
       <c r="T173" t="n">
@@ -17034,7 +17034,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>31-01-2021 08:30</t>
+          <t>2021-01-31 08:30:00</t>
         </is>
       </c>
       <c r="T174" t="inlineStr"/>
@@ -17127,7 +17127,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>13-02-2021 08:30</t>
+          <t>2021-02-13 08:30:00</t>
         </is>
       </c>
       <c r="T175" t="inlineStr"/>
@@ -17220,7 +17220,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T176" t="inlineStr"/>
@@ -17313,7 +17313,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T177" t="n">
@@ -17412,7 +17412,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>20-07-2021 08:30</t>
+          <t>2021-07-20 08:30:00</t>
         </is>
       </c>
       <c r="T178" t="n">
@@ -17511,7 +17511,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T179" t="n">
@@ -17610,7 +17610,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T180" t="inlineStr"/>
@@ -17703,7 +17703,7 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T181" t="inlineStr"/>
@@ -17796,7 +17796,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T182" t="inlineStr"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T183" t="inlineStr"/>
@@ -17982,7 +17982,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T184" t="inlineStr"/>
@@ -18075,7 +18075,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T185" t="inlineStr"/>
@@ -18168,7 +18168,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T186" t="inlineStr"/>
@@ -18261,7 +18261,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T187" t="inlineStr"/>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T188" t="inlineStr"/>
@@ -18447,7 +18447,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T189" t="inlineStr"/>
@@ -18540,7 +18540,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T190" t="inlineStr"/>
@@ -18633,7 +18633,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T191" t="n">
@@ -18728,7 +18728,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T192" t="n">
@@ -18823,7 +18823,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T193" t="n">
@@ -18918,7 +18918,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T194" t="n">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>26-05-2021 08:30</t>
+          <t>2021-05-26 08:30:00</t>
         </is>
       </c>
       <c r="T195" t="n">
@@ -19108,7 +19108,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>15-06-2021 08:30</t>
+          <t>2021-06-15 08:30:00</t>
         </is>
       </c>
       <c r="T196" t="n">
@@ -19203,7 +19203,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T197" t="n">
@@ -19298,7 +19298,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>12-08-2021 08:30</t>
+          <t>2021-12-08 08:30:00</t>
         </is>
       </c>
       <c r="T198" t="n">
@@ -19393,7 +19393,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>30-09-2021 08:30</t>
+          <t>2021-09-30 08:30:00</t>
         </is>
       </c>
       <c r="T199" t="n">
@@ -19488,7 +19488,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T200" t="n">
@@ -19583,7 +19583,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>25-11-2021 08:30</t>
+          <t>2021-11-25 08:30:00</t>
         </is>
       </c>
       <c r="T201" t="n">
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>10-12-2021 08:30</t>
+          <t>2021-10-12 08:30:00</t>
         </is>
       </c>
       <c r="T202" t="n">
@@ -19773,7 +19773,7 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T203" t="inlineStr"/>
@@ -19866,7 +19866,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T204" t="inlineStr"/>
@@ -19959,7 +19959,7 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T205" t="inlineStr"/>
@@ -20052,7 +20052,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T206" t="inlineStr"/>
@@ -20145,7 +20145,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T207" t="inlineStr"/>
@@ -20238,7 +20238,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T208" t="inlineStr"/>
@@ -20331,7 +20331,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T209" t="inlineStr"/>
@@ -20424,7 +20424,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T210" t="inlineStr"/>
@@ -20517,7 +20517,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T211" t="inlineStr"/>
@@ -20610,7 +20610,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T212" t="inlineStr"/>
@@ -20703,7 +20703,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>10-01-2021 08:30</t>
+          <t>2021-10-01 08:30:00</t>
         </is>
       </c>
       <c r="T213" t="inlineStr"/>
@@ -20796,7 +20796,7 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T214" t="inlineStr"/>
@@ -20889,7 +20889,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T215" t="inlineStr"/>
@@ -20982,7 +20982,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T216" t="n">
@@ -21081,7 +21081,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T217" t="n">
@@ -21180,7 +21180,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T218" t="inlineStr"/>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T219" t="inlineStr"/>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T220" t="inlineStr"/>
@@ -21459,7 +21459,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T221" t="inlineStr"/>
@@ -21552,7 +21552,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T222" t="inlineStr"/>
@@ -21645,7 +21645,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T223" t="inlineStr"/>
@@ -21738,7 +21738,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T224" t="inlineStr"/>
@@ -21831,7 +21831,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T225" t="inlineStr"/>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T226" t="inlineStr"/>
@@ -22017,7 +22017,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T227" t="inlineStr"/>
@@ -22110,7 +22110,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T228" t="inlineStr"/>
@@ -22203,7 +22203,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T229" t="inlineStr"/>
@@ -22296,7 +22296,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T230" t="inlineStr"/>
@@ -22389,7 +22389,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T231" t="inlineStr"/>
@@ -22482,7 +22482,7 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T232" t="inlineStr"/>
@@ -22575,7 +22575,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T233" t="inlineStr"/>
@@ -22668,7 +22668,7 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T234" t="inlineStr"/>
@@ -22761,7 +22761,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T235" t="inlineStr"/>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T236" t="inlineStr"/>
@@ -22947,7 +22947,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T237" t="inlineStr"/>
@@ -23040,7 +23040,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T238" t="inlineStr"/>
@@ -23133,7 +23133,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T239" t="inlineStr"/>
@@ -23226,7 +23226,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T240" t="inlineStr"/>
@@ -23319,7 +23319,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T241" t="inlineStr"/>
@@ -23412,7 +23412,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T242" t="inlineStr"/>
@@ -23505,7 +23505,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T243" t="inlineStr"/>
@@ -23598,7 +23598,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T244" t="inlineStr"/>
@@ -23691,7 +23691,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T245" t="inlineStr"/>
@@ -23784,7 +23784,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T246" t="inlineStr"/>
@@ -23877,7 +23877,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T247" t="inlineStr"/>
@@ -23970,7 +23970,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T248" t="inlineStr"/>
@@ -24063,7 +24063,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T249" t="inlineStr"/>
@@ -24156,7 +24156,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T250" t="inlineStr"/>
@@ -24249,7 +24249,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T251" t="inlineStr"/>
@@ -24342,7 +24342,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T252" t="inlineStr"/>
@@ -24435,7 +24435,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T253" t="inlineStr"/>
@@ -24528,7 +24528,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T254" t="inlineStr"/>
@@ -24621,7 +24621,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T255" t="inlineStr"/>
@@ -24714,7 +24714,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T256" t="inlineStr"/>
@@ -24807,7 +24807,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T257" t="inlineStr"/>
@@ -24900,7 +24900,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T258" t="inlineStr"/>
@@ -24993,7 +24993,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T259" t="inlineStr"/>
@@ -25086,7 +25086,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T260" t="inlineStr"/>
@@ -25179,7 +25179,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T261" t="inlineStr"/>
@@ -25272,7 +25272,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T262" t="inlineStr"/>
@@ -25365,7 +25365,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T263" t="inlineStr"/>
@@ -25458,7 +25458,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T264" t="inlineStr"/>
@@ -25551,7 +25551,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T265" t="inlineStr"/>
@@ -25644,7 +25644,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T266" t="inlineStr"/>
@@ -25737,7 +25737,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T267" t="inlineStr"/>
@@ -25830,7 +25830,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T268" t="inlineStr"/>
@@ -25923,7 +25923,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T269" t="inlineStr"/>
@@ -26016,7 +26016,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T270" t="inlineStr"/>
@@ -26109,7 +26109,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T271" t="inlineStr"/>
@@ -26202,7 +26202,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T272" t="inlineStr"/>
@@ -26295,7 +26295,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T273" t="inlineStr"/>
@@ -26388,7 +26388,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T274" t="inlineStr"/>
@@ -26481,7 +26481,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T275" t="inlineStr"/>
@@ -26574,7 +26574,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T276" t="inlineStr"/>
@@ -26667,7 +26667,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T277" t="inlineStr"/>
@@ -26760,7 +26760,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T278" t="inlineStr"/>
@@ -26853,7 +26853,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>03-01-2021 08:30</t>
+          <t>2021-03-01 08:30:00</t>
         </is>
       </c>
       <c r="T279" t="n">
@@ -26948,7 +26948,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T280" t="n">
@@ -27043,7 +27043,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T281" t="n">
@@ -27138,7 +27138,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T282" t="n">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>06-05-2021 08:30</t>
+          <t>2021-06-05 08:30:00</t>
         </is>
       </c>
       <c r="T283" t="n">
@@ -27328,7 +27328,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>04-06-2021 08:30</t>
+          <t>2021-04-06 08:30:00</t>
         </is>
       </c>
       <c r="T284" t="n">
@@ -27423,7 +27423,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T285" t="n">
@@ -27518,7 +27518,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>06-08-2021 08:30</t>
+          <t>2021-06-08 08:30:00</t>
         </is>
       </c>
       <c r="T286" t="n">
@@ -27613,7 +27613,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>09-09-2021 08:30</t>
+          <t>2021-09-09 08:30:00</t>
         </is>
       </c>
       <c r="T287" t="n">
@@ -27708,7 +27708,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>13-10-2021 08:30</t>
+          <t>2021-10-13 08:30:00</t>
         </is>
       </c>
       <c r="T288" t="n">
@@ -27803,7 +27803,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>09-11-2021 08:30</t>
+          <t>2021-09-11 08:30:00</t>
         </is>
       </c>
       <c r="T289" t="n">
@@ -27898,7 +27898,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>04-12-2021 08:30</t>
+          <t>2021-04-12 08:30:00</t>
         </is>
       </c>
       <c r="T290" t="n">
@@ -27993,7 +27993,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T291" t="inlineStr"/>
@@ -28086,7 +28086,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T292" t="inlineStr"/>
@@ -28179,7 +28179,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T293" t="inlineStr"/>
@@ -28272,7 +28272,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T294" t="inlineStr"/>
@@ -28365,7 +28365,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T295" t="inlineStr"/>
@@ -28458,7 +28458,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T296" t="inlineStr"/>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T297" t="inlineStr"/>
@@ -28644,7 +28644,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T298" t="inlineStr"/>
@@ -28737,7 +28737,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T299" t="inlineStr"/>
@@ -28830,7 +28830,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T300" t="inlineStr"/>
@@ -28923,7 +28923,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T301" t="inlineStr"/>
@@ -29016,7 +29016,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T302" t="inlineStr"/>
@@ -29109,7 +29109,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T303" t="inlineStr"/>
@@ -29202,7 +29202,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T304" t="inlineStr"/>
@@ -29295,7 +29295,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T305" t="inlineStr"/>
@@ -29388,7 +29388,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T306" t="inlineStr"/>
@@ -29481,7 +29481,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T307" t="inlineStr"/>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T308" t="inlineStr"/>
@@ -29667,7 +29667,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T309" t="inlineStr"/>
@@ -29760,7 +29760,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T310" t="inlineStr"/>
@@ -29853,7 +29853,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T311" t="inlineStr"/>
@@ -29946,7 +29946,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>09-01-2021 08:30</t>
+          <t>2021-09-01 08:30:00</t>
         </is>
       </c>
       <c r="T312" t="inlineStr"/>
@@ -30039,7 +30039,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>14-02-2021 08:30</t>
+          <t>2021-02-14 08:30:00</t>
         </is>
       </c>
       <c r="T313" t="inlineStr"/>
@@ -30132,7 +30132,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T314" t="inlineStr"/>
@@ -30225,7 +30225,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T315" t="n">
@@ -30320,7 +30320,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T316" t="n">
@@ -30415,7 +30415,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T317" t="n">
@@ -30510,7 +30510,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T318" t="n">
@@ -30605,7 +30605,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>14-05-2021 08:30</t>
+          <t>2021-05-14 08:30:00</t>
         </is>
       </c>
       <c r="T319" t="n">
@@ -30700,7 +30700,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>04-06-2021 08:30</t>
+          <t>2021-04-06 08:30:00</t>
         </is>
       </c>
       <c r="T320" t="n">
@@ -30795,7 +30795,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T321" t="n">
@@ -30890,7 +30890,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T322" t="n">
@@ -30985,7 +30985,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T323" t="n">
@@ -31080,7 +31080,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T324" t="n">
@@ -31175,7 +31175,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T325" t="n">
@@ -31270,7 +31270,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>04-12-2021 08:30</t>
+          <t>2021-04-12 08:30:00</t>
         </is>
       </c>
       <c r="T326" t="n">
@@ -31365,7 +31365,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T327" t="inlineStr"/>
@@ -31458,7 +31458,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T328" t="inlineStr"/>
@@ -31551,7 +31551,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T329" t="inlineStr"/>
@@ -31644,7 +31644,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T330" t="inlineStr"/>
@@ -31737,7 +31737,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T331" t="inlineStr"/>
@@ -31830,7 +31830,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T332" t="inlineStr"/>
@@ -31923,7 +31923,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T333" t="inlineStr"/>
@@ -32016,7 +32016,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T334" t="inlineStr"/>
@@ -32109,7 +32109,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T335" t="inlineStr"/>
@@ -32202,7 +32202,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T336" t="inlineStr"/>
@@ -32295,7 +32295,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T337" t="inlineStr"/>
@@ -32388,7 +32388,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T338" t="inlineStr"/>
@@ -32481,7 +32481,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T339" t="inlineStr"/>
@@ -32574,7 +32574,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T340" t="inlineStr"/>
@@ -32667,7 +32667,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T341" t="inlineStr"/>
@@ -32760,7 +32760,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T342" t="inlineStr"/>
@@ -32853,7 +32853,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T343" t="inlineStr"/>
@@ -32946,7 +32946,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T344" t="inlineStr"/>
@@ -33039,7 +33039,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T345" t="inlineStr"/>
@@ -33132,7 +33132,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T346" t="inlineStr"/>
@@ -33225,7 +33225,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T347" t="inlineStr"/>
@@ -33318,7 +33318,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T348" t="inlineStr"/>
@@ -33411,7 +33411,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T349" t="inlineStr"/>
@@ -33504,7 +33504,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T350" t="inlineStr"/>
@@ -33597,7 +33597,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T351" t="inlineStr"/>
@@ -33690,7 +33690,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T352" t="inlineStr"/>
@@ -33783,7 +33783,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T353" t="inlineStr"/>
@@ -33876,7 +33876,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T354" t="inlineStr"/>
@@ -33969,7 +33969,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T355" t="inlineStr"/>
@@ -34062,7 +34062,7 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T356" t="inlineStr"/>
@@ -34155,7 +34155,7 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T357" t="inlineStr"/>
@@ -34248,7 +34248,7 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T358" t="inlineStr"/>
@@ -34341,7 +34341,7 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T359" t="inlineStr"/>
@@ -34434,7 +34434,7 @@
       </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T360" t="inlineStr"/>
@@ -34527,7 +34527,7 @@
       </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T361" t="inlineStr"/>
@@ -34620,7 +34620,7 @@
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T362" t="inlineStr"/>
@@ -34713,7 +34713,7 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T363" t="inlineStr"/>
@@ -34806,7 +34806,7 @@
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T364" t="inlineStr"/>
@@ -34899,7 +34899,7 @@
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T365" t="inlineStr"/>
@@ -34992,7 +34992,7 @@
       </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T366" t="inlineStr"/>
@@ -35085,7 +35085,7 @@
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T367" t="inlineStr"/>
@@ -35178,7 +35178,7 @@
       </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T368" t="inlineStr"/>
@@ -35271,7 +35271,7 @@
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T369" t="inlineStr"/>
@@ -35364,7 +35364,7 @@
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T370" t="inlineStr"/>
@@ -35457,7 +35457,7 @@
       </c>
       <c r="S371" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T371" t="inlineStr"/>
@@ -35550,7 +35550,7 @@
       </c>
       <c r="S372" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T372" t="inlineStr"/>
@@ -35643,7 +35643,7 @@
       </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T373" t="inlineStr"/>
@@ -35736,7 +35736,7 @@
       </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T374" t="inlineStr"/>
@@ -35829,7 +35829,7 @@
       </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T375" t="inlineStr"/>
@@ -35922,7 +35922,7 @@
       </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T376" t="inlineStr"/>
@@ -36015,7 +36015,7 @@
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T377" t="inlineStr"/>
@@ -36108,7 +36108,7 @@
       </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T378" t="inlineStr"/>
@@ -36201,7 +36201,7 @@
       </c>
       <c r="S379" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T379" t="inlineStr"/>
@@ -36294,7 +36294,7 @@
       </c>
       <c r="S380" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T380" t="inlineStr"/>
@@ -36387,7 +36387,7 @@
       </c>
       <c r="S381" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T381" t="inlineStr"/>
@@ -36480,7 +36480,7 @@
       </c>
       <c r="S382" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T382" t="inlineStr"/>
@@ -36573,7 +36573,7 @@
       </c>
       <c r="S383" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T383" t="inlineStr"/>
@@ -36666,7 +36666,7 @@
       </c>
       <c r="S384" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T384" t="inlineStr"/>
@@ -36759,7 +36759,7 @@
       </c>
       <c r="S385" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T385" t="inlineStr"/>
@@ -36852,7 +36852,7 @@
       </c>
       <c r="S386" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T386" t="inlineStr"/>
@@ -36945,7 +36945,7 @@
       </c>
       <c r="S387" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T387" t="inlineStr"/>
@@ -37038,7 +37038,7 @@
       </c>
       <c r="S388" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T388" t="inlineStr"/>
@@ -37131,7 +37131,7 @@
       </c>
       <c r="S389" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T389" t="inlineStr"/>
@@ -37224,7 +37224,7 @@
       </c>
       <c r="S390" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T390" t="inlineStr"/>
@@ -37317,7 +37317,7 @@
       </c>
       <c r="S391" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T391" t="inlineStr"/>
@@ -37410,7 +37410,7 @@
       </c>
       <c r="S392" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T392" t="inlineStr"/>
@@ -37503,7 +37503,7 @@
       </c>
       <c r="S393" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T393" t="inlineStr"/>
@@ -37596,7 +37596,7 @@
       </c>
       <c r="S394" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T394" t="inlineStr"/>
@@ -37689,7 +37689,7 @@
       </c>
       <c r="S395" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T395" t="inlineStr"/>
@@ -37782,7 +37782,7 @@
       </c>
       <c r="S396" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T396" t="inlineStr"/>
@@ -37875,7 +37875,7 @@
       </c>
       <c r="S397" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T397" t="inlineStr"/>
@@ -37968,7 +37968,7 @@
       </c>
       <c r="S398" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T398" t="inlineStr"/>
@@ -38061,7 +38061,7 @@
       </c>
       <c r="S399" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T399" t="inlineStr"/>
@@ -38154,7 +38154,7 @@
       </c>
       <c r="S400" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T400" t="inlineStr"/>
@@ -38247,7 +38247,7 @@
       </c>
       <c r="S401" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T401" t="inlineStr"/>
@@ -38340,7 +38340,7 @@
       </c>
       <c r="S402" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T402" t="inlineStr"/>
@@ -38433,7 +38433,7 @@
       </c>
       <c r="S403" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T403" t="inlineStr"/>
@@ -38526,7 +38526,7 @@
       </c>
       <c r="S404" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T404" t="inlineStr"/>
@@ -38619,7 +38619,7 @@
       </c>
       <c r="S405" t="inlineStr">
         <is>
-          <t>30-01-2021 08:30</t>
+          <t>2021-01-30 08:30:00</t>
         </is>
       </c>
       <c r="T405" t="n">
@@ -38714,7 +38714,7 @@
       </c>
       <c r="S406" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T406" t="n">
@@ -38809,7 +38809,7 @@
       </c>
       <c r="S407" t="inlineStr">
         <is>
-          <t>27-03-2021 08:30</t>
+          <t>2021-03-27 08:30:00</t>
         </is>
       </c>
       <c r="T407" t="n">
@@ -38904,7 +38904,7 @@
       </c>
       <c r="S408" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T408" t="n">
@@ -38999,7 +38999,7 @@
       </c>
       <c r="S409" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T409" t="n">
@@ -39094,7 +39094,7 @@
       </c>
       <c r="S410" t="inlineStr">
         <is>
-          <t>30-06-2021 08:30</t>
+          <t>2021-06-30 08:30:00</t>
         </is>
       </c>
       <c r="T410" t="n">
@@ -39189,7 +39189,7 @@
       </c>
       <c r="S411" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T411" t="n">
@@ -39284,7 +39284,7 @@
       </c>
       <c r="S412" t="inlineStr">
         <is>
-          <t>31-08-2021 08:30</t>
+          <t>2021-08-31 08:30:00</t>
         </is>
       </c>
       <c r="T412" t="n">
@@ -39379,7 +39379,7 @@
       </c>
       <c r="S413" t="inlineStr">
         <is>
-          <t>25-09-2021 08:30</t>
+          <t>2021-09-25 08:30:00</t>
         </is>
       </c>
       <c r="T413" t="n">
@@ -39474,7 +39474,7 @@
       </c>
       <c r="S414" t="inlineStr">
         <is>
-          <t>13-10-2021 08:30</t>
+          <t>2021-10-13 08:30:00</t>
         </is>
       </c>
       <c r="T414" t="n">
@@ -39569,7 +39569,7 @@
       </c>
       <c r="S415" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T415" t="n">
@@ -39664,7 +39664,7 @@
       </c>
       <c r="S416" t="inlineStr">
         <is>
-          <t>30-12-2021 08:30</t>
+          <t>2021-12-30 08:30:00</t>
         </is>
       </c>
       <c r="T416" t="n">
@@ -39759,7 +39759,7 @@
       </c>
       <c r="S417" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T417" t="inlineStr"/>
@@ -39852,7 +39852,7 @@
       </c>
       <c r="S418" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T418" t="inlineStr"/>
@@ -39945,7 +39945,7 @@
       </c>
       <c r="S419" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T419" t="inlineStr"/>
@@ -40038,7 +40038,7 @@
       </c>
       <c r="S420" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T420" t="inlineStr"/>
@@ -40131,7 +40131,7 @@
       </c>
       <c r="S421" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T421" t="inlineStr"/>
@@ -40224,7 +40224,7 @@
       </c>
       <c r="S422" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T422" t="inlineStr"/>
@@ -40317,7 +40317,7 @@
       </c>
       <c r="S423" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T423" t="inlineStr"/>
@@ -40410,7 +40410,7 @@
       </c>
       <c r="S424" t="inlineStr">
         <is>
-          <t>09-01-2021 08:30</t>
+          <t>2021-09-01 08:30:00</t>
         </is>
       </c>
       <c r="T424" t="inlineStr"/>
@@ -40503,7 +40503,7 @@
       </c>
       <c r="S425" t="inlineStr">
         <is>
-          <t>14-02-2021 08:30</t>
+          <t>2021-02-14 08:30:00</t>
         </is>
       </c>
       <c r="T425" t="inlineStr"/>
@@ -40596,7 +40596,7 @@
       </c>
       <c r="S426" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T426" t="inlineStr"/>
@@ -40689,7 +40689,7 @@
       </c>
       <c r="S427" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T427" t="inlineStr"/>
@@ -40782,7 +40782,7 @@
       </c>
       <c r="S428" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T428" t="inlineStr"/>
@@ -40875,7 +40875,7 @@
       </c>
       <c r="S429" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T429" t="inlineStr"/>
@@ -40968,7 +40968,7 @@
       </c>
       <c r="S430" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T430" t="inlineStr"/>
@@ -41061,7 +41061,7 @@
       </c>
       <c r="S431" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T431" t="inlineStr"/>
@@ -41154,7 +41154,7 @@
       </c>
       <c r="S432" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T432" t="inlineStr"/>
@@ -41247,7 +41247,7 @@
       </c>
       <c r="S433" t="inlineStr">
         <is>
-          <t>03-01-2021 08:30</t>
+          <t>2021-03-01 08:30:00</t>
         </is>
       </c>
       <c r="T433" t="inlineStr"/>
@@ -41340,7 +41340,7 @@
       </c>
       <c r="S434" t="inlineStr">
         <is>
-          <t>07-02-2021 08:30</t>
+          <t>2021-07-02 08:30:00</t>
         </is>
       </c>
       <c r="T434" t="inlineStr"/>
@@ -41433,7 +41433,7 @@
       </c>
       <c r="S435" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T435" t="inlineStr"/>
@@ -41526,7 +41526,7 @@
       </c>
       <c r="S436" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T436" t="inlineStr"/>
@@ -41619,7 +41619,7 @@
       </c>
       <c r="S437" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T437" t="inlineStr"/>
@@ -41712,7 +41712,7 @@
       </c>
       <c r="S438" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T438" t="inlineStr"/>
@@ -41805,7 +41805,7 @@
       </c>
       <c r="S439" t="inlineStr">
         <is>
-          <t>31-01-2021 08:30</t>
+          <t>2021-01-31 08:30:00</t>
         </is>
       </c>
       <c r="T439" t="inlineStr"/>
@@ -41898,7 +41898,7 @@
       </c>
       <c r="S440" t="inlineStr">
         <is>
-          <t>13-02-2021 08:30</t>
+          <t>2021-02-13 08:30:00</t>
         </is>
       </c>
       <c r="T440" t="inlineStr"/>
@@ -41991,7 +41991,7 @@
       </c>
       <c r="S441" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T441" t="inlineStr"/>
@@ -42084,7 +42084,7 @@
       </c>
       <c r="S442" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T442" t="inlineStr"/>
@@ -42177,7 +42177,7 @@
       </c>
       <c r="S443" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T443" t="inlineStr"/>
@@ -42270,7 +42270,7 @@
       </c>
       <c r="S444" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T444" t="inlineStr"/>
@@ -42363,7 +42363,7 @@
       </c>
       <c r="S445" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T445" t="inlineStr"/>
@@ -42456,7 +42456,7 @@
       </c>
       <c r="S446" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T446" t="inlineStr"/>
@@ -42549,7 +42549,7 @@
       </c>
       <c r="S447" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T447" t="inlineStr"/>
@@ -42642,7 +42642,7 @@
       </c>
       <c r="S448" t="inlineStr">
         <is>
-          <t>31-01-2021 08:30</t>
+          <t>2021-01-31 08:30:00</t>
         </is>
       </c>
       <c r="T448" t="inlineStr"/>
@@ -42735,7 +42735,7 @@
       </c>
       <c r="S449" t="inlineStr">
         <is>
-          <t>13-02-2021 08:30</t>
+          <t>2021-02-13 08:30:00</t>
         </is>
       </c>
       <c r="T449" t="inlineStr"/>
@@ -42828,7 +42828,7 @@
       </c>
       <c r="S450" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T450" t="inlineStr"/>
@@ -42921,7 +42921,7 @@
       </c>
       <c r="S451" t="inlineStr">
         <is>
-          <t>03-01-2021 08:30</t>
+          <t>2021-03-01 08:30:00</t>
         </is>
       </c>
       <c r="T451" t="inlineStr"/>
@@ -43014,7 +43014,7 @@
       </c>
       <c r="S452" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T452" t="inlineStr"/>
@@ -43107,7 +43107,7 @@
       </c>
       <c r="S453" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T453" t="inlineStr"/>
@@ -43200,7 +43200,7 @@
       </c>
       <c r="S454" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T454" t="inlineStr"/>
@@ -43293,7 +43293,7 @@
       </c>
       <c r="S455" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T455" t="inlineStr"/>
@@ -43386,7 +43386,7 @@
       </c>
       <c r="S456" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T456" t="inlineStr"/>
@@ -43479,7 +43479,7 @@
       </c>
       <c r="S457" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T457" t="inlineStr"/>
@@ -43572,7 +43572,7 @@
       </c>
       <c r="S458" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T458" t="inlineStr"/>
@@ -43665,7 +43665,7 @@
       </c>
       <c r="S459" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T459" t="inlineStr"/>
@@ -43758,7 +43758,7 @@
       </c>
       <c r="S460" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T460" t="inlineStr"/>
@@ -43851,7 +43851,7 @@
       </c>
       <c r="S461" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T461" t="inlineStr"/>
@@ -43944,7 +43944,7 @@
       </c>
       <c r="S462" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T462" t="inlineStr"/>
@@ -44037,7 +44037,7 @@
       </c>
       <c r="S463" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T463" t="inlineStr"/>
@@ -44130,7 +44130,7 @@
       </c>
       <c r="S464" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T464" t="inlineStr"/>
@@ -44223,7 +44223,7 @@
       </c>
       <c r="S465" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T465" t="inlineStr"/>
@@ -44316,7 +44316,7 @@
       </c>
       <c r="S466" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T466" t="inlineStr"/>
@@ -44409,7 +44409,7 @@
       </c>
       <c r="S467" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T467" t="inlineStr"/>
@@ -44502,7 +44502,7 @@
       </c>
       <c r="S468" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T468" t="inlineStr"/>
@@ -44595,7 +44595,7 @@
       </c>
       <c r="S469" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T469" t="inlineStr"/>
@@ -44688,7 +44688,7 @@
       </c>
       <c r="S470" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T470" t="inlineStr"/>
@@ -44781,7 +44781,7 @@
       </c>
       <c r="S471" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T471" t="inlineStr"/>
@@ -44874,7 +44874,7 @@
       </c>
       <c r="S472" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T472" t="inlineStr"/>
@@ -44967,7 +44967,7 @@
       </c>
       <c r="S473" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T473" t="inlineStr"/>
@@ -45060,7 +45060,7 @@
       </c>
       <c r="S474" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T474" t="inlineStr"/>
@@ -45153,7 +45153,7 @@
       </c>
       <c r="S475" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T475" t="inlineStr"/>
@@ -45246,7 +45246,7 @@
       </c>
       <c r="S476" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T476" t="inlineStr"/>
@@ -45339,7 +45339,7 @@
       </c>
       <c r="S477" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T477" t="inlineStr"/>
@@ -45432,7 +45432,7 @@
       </c>
       <c r="S478" t="inlineStr">
         <is>
-          <t>30-01-2021 08:30</t>
+          <t>2021-01-30 08:30:00</t>
         </is>
       </c>
       <c r="T478" t="inlineStr"/>
@@ -45525,7 +45525,7 @@
       </c>
       <c r="S479" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T479" t="inlineStr"/>
@@ -45618,7 +45618,7 @@
       </c>
       <c r="S480" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T480" t="inlineStr"/>
@@ -45711,7 +45711,7 @@
       </c>
       <c r="S481" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T481" t="inlineStr"/>
@@ -45804,7 +45804,7 @@
       </c>
       <c r="S482" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T482" t="inlineStr"/>
@@ -45897,7 +45897,7 @@
       </c>
       <c r="S483" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T483" t="inlineStr"/>
@@ -45990,7 +45990,7 @@
       </c>
       <c r="S484" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T484" t="inlineStr"/>
@@ -46083,7 +46083,7 @@
       </c>
       <c r="S485" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T485" t="inlineStr"/>
@@ -46176,7 +46176,7 @@
       </c>
       <c r="S486" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T486" t="inlineStr"/>
@@ -46269,7 +46269,7 @@
       </c>
       <c r="S487" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T487" t="inlineStr"/>
@@ -46362,7 +46362,7 @@
       </c>
       <c r="S488" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T488" t="inlineStr"/>
@@ -46455,7 +46455,7 @@
       </c>
       <c r="S489" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T489" t="inlineStr"/>
@@ -46548,7 +46548,7 @@
       </c>
       <c r="S490" t="inlineStr">
         <is>
-          <t>03-01-2021 08:30</t>
+          <t>2021-03-01 08:30:00</t>
         </is>
       </c>
       <c r="T490" t="inlineStr"/>
@@ -46641,7 +46641,7 @@
       </c>
       <c r="S491" t="inlineStr">
         <is>
-          <t>07-02-2021 08:30</t>
+          <t>2021-07-02 08:30:00</t>
         </is>
       </c>
       <c r="T491" t="inlineStr"/>
@@ -46734,7 +46734,7 @@
       </c>
       <c r="S492" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T492" t="inlineStr"/>
@@ -46827,7 +46827,7 @@
       </c>
       <c r="S493" t="inlineStr">
         <is>
-          <t>03-01-2021 08:30</t>
+          <t>2021-03-01 08:30:00</t>
         </is>
       </c>
       <c r="T493" t="inlineStr"/>
@@ -46920,7 +46920,7 @@
       </c>
       <c r="S494" t="inlineStr">
         <is>
-          <t>07-02-2021 08:30</t>
+          <t>2021-07-02 08:30:00</t>
         </is>
       </c>
       <c r="T494" t="inlineStr"/>
@@ -47013,7 +47013,7 @@
       </c>
       <c r="S495" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T495" t="inlineStr"/>
@@ -47106,7 +47106,7 @@
       </c>
       <c r="S496" t="inlineStr">
         <is>
-          <t>03-01-2021 08:30</t>
+          <t>2021-03-01 08:30:00</t>
         </is>
       </c>
       <c r="T496" t="inlineStr"/>
@@ -47199,7 +47199,7 @@
       </c>
       <c r="S497" t="inlineStr">
         <is>
-          <t>07-02-2021 08:30</t>
+          <t>2021-07-02 08:30:00</t>
         </is>
       </c>
       <c r="T497" t="inlineStr"/>
@@ -47292,7 +47292,7 @@
       </c>
       <c r="S498" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T498" t="inlineStr"/>
@@ -47385,7 +47385,7 @@
       </c>
       <c r="S499" t="inlineStr">
         <is>
-          <t>03-01-2021 08:30</t>
+          <t>2021-03-01 08:30:00</t>
         </is>
       </c>
       <c r="T499" t="inlineStr"/>
@@ -47478,7 +47478,7 @@
       </c>
       <c r="S500" t="inlineStr">
         <is>
-          <t>07-02-2021 08:30</t>
+          <t>2021-07-02 08:30:00</t>
         </is>
       </c>
       <c r="T500" t="inlineStr"/>
@@ -47571,7 +47571,7 @@
       </c>
       <c r="S501" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T501" t="inlineStr"/>
@@ -47664,7 +47664,7 @@
       </c>
       <c r="S502" t="inlineStr">
         <is>
-          <t>03-01-2021 08:30</t>
+          <t>2021-03-01 08:30:00</t>
         </is>
       </c>
       <c r="T502" t="inlineStr"/>
@@ -47757,7 +47757,7 @@
       </c>
       <c r="S503" t="inlineStr">
         <is>
-          <t>07-02-2021 08:30</t>
+          <t>2021-07-02 08:30:00</t>
         </is>
       </c>
       <c r="T503" t="inlineStr"/>
@@ -47850,7 +47850,7 @@
       </c>
       <c r="S504" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T504" t="inlineStr"/>
@@ -47943,7 +47943,7 @@
       </c>
       <c r="S505" t="inlineStr">
         <is>
-          <t>03-01-2021 08:30</t>
+          <t>2021-03-01 08:30:00</t>
         </is>
       </c>
       <c r="T505" t="inlineStr"/>
@@ -48036,7 +48036,7 @@
       </c>
       <c r="S506" t="inlineStr">
         <is>
-          <t>07-02-2021 08:30</t>
+          <t>2021-07-02 08:30:00</t>
         </is>
       </c>
       <c r="T506" t="inlineStr"/>
@@ -48129,7 +48129,7 @@
       </c>
       <c r="S507" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T507" t="inlineStr"/>
@@ -48222,7 +48222,7 @@
       </c>
       <c r="S508" t="inlineStr">
         <is>
-          <t>03-01-2021 08:30</t>
+          <t>2021-03-01 08:30:00</t>
         </is>
       </c>
       <c r="T508" t="inlineStr"/>
@@ -48315,7 +48315,7 @@
       </c>
       <c r="S509" t="inlineStr">
         <is>
-          <t>07-02-2021 08:30</t>
+          <t>2021-07-02 08:30:00</t>
         </is>
       </c>
       <c r="T509" t="inlineStr"/>
@@ -48408,7 +48408,7 @@
       </c>
       <c r="S510" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T510" t="inlineStr"/>
@@ -48501,7 +48501,7 @@
       </c>
       <c r="S511" t="inlineStr">
         <is>
-          <t>03-01-2021 08:30</t>
+          <t>2021-03-01 08:30:00</t>
         </is>
       </c>
       <c r="T511" t="inlineStr"/>
@@ -48594,7 +48594,7 @@
       </c>
       <c r="S512" t="inlineStr">
         <is>
-          <t>07-02-2021 08:30</t>
+          <t>2021-07-02 08:30:00</t>
         </is>
       </c>
       <c r="T512" t="inlineStr"/>
@@ -48687,7 +48687,7 @@
       </c>
       <c r="S513" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T513" t="inlineStr"/>
@@ -48780,7 +48780,7 @@
       </c>
       <c r="S514" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T514" t="inlineStr"/>
@@ -48873,7 +48873,7 @@
       </c>
       <c r="S515" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T515" t="inlineStr"/>
@@ -48966,7 +48966,7 @@
       </c>
       <c r="S516" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T516" t="inlineStr"/>
@@ -49059,7 +49059,7 @@
       </c>
       <c r="S517" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T517" t="inlineStr"/>
@@ -49152,7 +49152,7 @@
       </c>
       <c r="S518" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T518" t="inlineStr"/>
@@ -49245,7 +49245,7 @@
       </c>
       <c r="S519" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T519" t="inlineStr"/>
@@ -49338,7 +49338,7 @@
       </c>
       <c r="S520" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T520" t="inlineStr"/>
@@ -49431,7 +49431,7 @@
       </c>
       <c r="S521" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T521" t="inlineStr"/>
@@ -49524,7 +49524,7 @@
       </c>
       <c r="S522" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T522" t="inlineStr"/>
@@ -49617,7 +49617,7 @@
       </c>
       <c r="S523" t="inlineStr">
         <is>
-          <t>10-01-2021 08:30</t>
+          <t>2021-10-01 08:30:00</t>
         </is>
       </c>
       <c r="T523" t="inlineStr"/>
@@ -49710,7 +49710,7 @@
       </c>
       <c r="S524" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T524" t="inlineStr"/>
@@ -49803,7 +49803,7 @@
       </c>
       <c r="S525" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T525" t="inlineStr"/>
@@ -49896,7 +49896,7 @@
       </c>
       <c r="S526" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T526" t="n">
@@ -49995,7 +49995,7 @@
       </c>
       <c r="S527" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T527" t="n">
@@ -50094,7 +50094,7 @@
       </c>
       <c r="S528" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T528" t="n">
@@ -50193,7 +50193,7 @@
       </c>
       <c r="S529" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T529" t="n">
@@ -50292,7 +50292,7 @@
       </c>
       <c r="S530" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T530" t="n">
@@ -50391,7 +50391,7 @@
       </c>
       <c r="S531" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T531" t="n">
@@ -50490,7 +50490,7 @@
       </c>
       <c r="S532" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T532" t="n">
@@ -50589,7 +50589,7 @@
       </c>
       <c r="S533" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T533" t="n">
@@ -50688,7 +50688,7 @@
       </c>
       <c r="S534" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T534" t="n">
@@ -50787,7 +50787,7 @@
       </c>
       <c r="S535" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T535" t="n">
@@ -50886,7 +50886,7 @@
       </c>
       <c r="S536" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T536" t="n">
@@ -50985,7 +50985,7 @@
       </c>
       <c r="S537" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T537" t="n">
@@ -51084,7 +51084,7 @@
       </c>
       <c r="S538" t="inlineStr">
         <is>
-          <t>13-10-2021 08:30</t>
+          <t>2021-10-13 08:30:00</t>
         </is>
       </c>
       <c r="T538" t="n">
@@ -51183,7 +51183,7 @@
       </c>
       <c r="S539" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T539" t="inlineStr"/>
@@ -51276,7 +51276,7 @@
       </c>
       <c r="S540" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T540" t="inlineStr"/>
@@ -51369,7 +51369,7 @@
       </c>
       <c r="S541" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T541" t="inlineStr"/>
@@ -51462,7 +51462,7 @@
       </c>
       <c r="S542" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T542" t="inlineStr"/>
@@ -51555,7 +51555,7 @@
       </c>
       <c r="S543" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T543" t="inlineStr"/>
@@ -51648,7 +51648,7 @@
       </c>
       <c r="S544" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T544" t="inlineStr"/>
@@ -51741,7 +51741,7 @@
       </c>
       <c r="S545" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T545" t="inlineStr"/>
@@ -51834,7 +51834,7 @@
       </c>
       <c r="S546" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T546" t="inlineStr"/>
